--- a/excel-files/PARANAQUE/MARCELO GREEN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PARANAQUE/MARCELO GREEN ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E11CA38-255B-4A73-AE50-77FB3FD0034C}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8087D86-6BA0-460D-B818-9027E4D5FF7E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -692,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,23 +773,14 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -803,21 +794,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -827,7 +803,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -838,6 +813,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1815,7 +1835,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color rgb="FF000000"/>
@@ -1851,8 +1871,8 @@
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1891,7 +1911,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -2953,7 +2973,7 @@
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -5424,8 +5444,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5440,7 +5460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5470,38 +5490,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="52" t="s">
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="53" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="54" t="s">
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5540,10 +5560,10 @@
       <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="37" t="s">
         <v>46</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5576,10 +5596,10 @@
       <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="48" t="s">
+      <c r="Y2" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="48" t="s">
+      <c r="Z2" s="38" t="s">
         <v>58</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5587,33 +5607,33 @@
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34">
+      <c r="B3" s="44"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>0</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="32">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
-      <c r="J3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="34"/>
+      <c r="J3" s="32">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="32"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
@@ -5626,42 +5646,59 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34">
+      <c r="Q3" s="32"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>0</v>
       </c>
-      <c r="U3" s="34">
+      <c r="U3" s="32">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
-      <c r="V3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="34"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34">
+      <c r="V3" s="32">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="32"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="34">
+      <c r="AA3" s="32">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
       <c r="J4" s="13"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="45"/>
       <c r="S4" s="5"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="45"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
@@ -5669,26 +5706,26 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="40">
+      <c r="D5" s="47">
         <v>341</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="47">
         <v>176</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="48">
         <v>2024</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="47">
         <v>165</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="47">
         <v>341</v>
       </c>
       <c r="J5" s="5">
@@ -5741,26 +5778,26 @@
       <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="40">
+      <c r="D6" s="47">
         <v>341</v>
       </c>
-      <c r="E6" s="40">
-        <v>0</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="40">
+      <c r="E6" s="47">
+        <v>0</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="47">
         <v>0</v>
       </c>
       <c r="J6" s="5">
@@ -5813,26 +5850,26 @@
       <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="40">
+      <c r="D7" s="47">
         <v>341</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="47">
         <v>300</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="48">
         <v>2024</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="47">
         <v>41</v>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="47">
         <v>341</v>
       </c>
       <c r="J7" s="5">
@@ -5885,26 +5922,26 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="40">
+      <c r="D8" s="47">
         <v>341</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="47">
         <v>300</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="48">
         <v>2024</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="47">
         <v>41</v>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="47">
         <v>341</v>
       </c>
       <c r="J8" s="5">
@@ -5957,26 +5994,26 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="40">
+      <c r="D9" s="47">
         <v>341</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="47">
         <v>300</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="48">
         <v>2024</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="47">
         <v>41</v>
       </c>
-      <c r="I9" s="40">
+      <c r="I9" s="47">
         <v>341</v>
       </c>
       <c r="J9" s="5">
@@ -6029,26 +6066,26 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="40">
+      <c r="D10" s="47">
         <v>341</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="47">
         <v>300</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="48">
         <v>2024</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="47">
         <v>41</v>
       </c>
-      <c r="I10" s="40">
+      <c r="I10" s="47">
         <v>341</v>
       </c>
       <c r="J10" s="5">
@@ -6101,26 +6138,26 @@
       <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="40">
+      <c r="D11" s="47">
         <v>341</v>
       </c>
-      <c r="E11" s="40">
-        <v>0</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="40">
+      <c r="E11" s="47">
+        <v>0</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="47">
         <v>0</v>
       </c>
       <c r="J11" s="5">
@@ -6173,26 +6210,26 @@
       <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="40">
+      <c r="D12" s="47">
         <v>341</v>
       </c>
-      <c r="E12" s="40">
-        <v>0</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="40">
+      <c r="E12" s="47">
+        <v>0</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="47">
         <v>0</v>
       </c>
       <c r="J12" s="5">
@@ -6242,32 +6279,42 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D13" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="42" t="s">
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="49" t="s">
         <v>62</v>
       </c>
       <c r="J13" s="13"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="45"/>
       <c r="S13" s="5"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
@@ -6276,26 +6323,26 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="40">
+      <c r="D14" s="47">
         <v>379</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="40">
+      <c r="E14" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="47">
         <v>0</v>
       </c>
       <c r="J14" s="5">
@@ -6348,26 +6395,26 @@
       <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="40">
+      <c r="D15" s="47">
         <v>379</v>
       </c>
-      <c r="E15" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="40">
+      <c r="E15" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="47">
         <v>0</v>
       </c>
       <c r="J15" s="5">
@@ -6420,26 +6467,26 @@
       <c r="A16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="40">
+      <c r="D16" s="47">
         <v>379</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="40">
+      <c r="E16" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="47">
         <v>0</v>
       </c>
       <c r="J16" s="5">
@@ -6492,42 +6539,48 @@
       <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="40">
+      <c r="D17" s="47">
         <v>379</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="47">
         <v>381</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="48">
         <v>2025</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="40">
+      <c r="H17" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="47">
         <v>2</v>
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+      <c r="K17" s="5">
+        <v>381</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -6564,26 +6617,26 @@
       <c r="A18" s="1">
         <v>2</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="40">
+      <c r="D18" s="47">
         <v>379</v>
       </c>
-      <c r="E18" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="40">
+      <c r="E18" s="47">
+        <v>302</v>
+      </c>
+      <c r="F18" s="48">
+        <v>2025</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="47">
         <v>0</v>
       </c>
       <c r="J18" s="5">
@@ -6636,42 +6689,48 @@
       <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="40">
+      <c r="D19" s="47">
         <v>379</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="47">
         <v>381</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="48">
         <v>2025</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="40">
+      <c r="H19" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="47">
         <v>2</v>
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="5"/>
+      <c r="K19" s="5">
+        <v>381</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="N19" s="5">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -6708,26 +6767,26 @@
       <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="40">
+      <c r="D20" s="47">
         <v>379</v>
       </c>
-      <c r="E20" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="40">
+      <c r="E20" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="47">
         <v>0</v>
       </c>
       <c r="J20" s="5">
@@ -6780,26 +6839,26 @@
       <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="40">
+      <c r="D21" s="47">
         <v>379</v>
       </c>
-      <c r="E21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="40">
+      <c r="E21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="47">
         <v>0</v>
       </c>
       <c r="J21" s="5">
@@ -6849,33 +6908,42 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D22" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="42" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="49" t="s">
         <v>62</v>
       </c>
       <c r="J22" s="13"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45"/>
       <c r="S22" s="5"/>
       <c r="T22" s="13"/>
       <c r="U22" s="13"/>
       <c r="V22" s="13"/>
+      <c r="W22" s="45"/>
+      <c r="X22" s="45"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
@@ -6884,26 +6952,26 @@
       <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="40">
+      <c r="D23" s="47">
         <v>411</v>
       </c>
-      <c r="E23" s="40">
-        <v>0</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="40">
+      <c r="E23" s="47">
+        <v>0</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="47">
         <v>0</v>
       </c>
       <c r="J23" s="5">
@@ -6956,26 +7024,26 @@
       <c r="A24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="40">
+      <c r="D24" s="47">
         <v>411</v>
       </c>
-      <c r="E24" s="40">
-        <v>0</v>
-      </c>
-      <c r="F24" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="40">
+      <c r="E24" s="47">
+        <v>0</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="47">
         <v>0</v>
       </c>
       <c r="J24" s="5">
@@ -7028,26 +7096,26 @@
       <c r="A25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="1"/>
-      <c r="D25" s="40">
+      <c r="D25" s="47">
         <v>411</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="47">
         <v>330</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="48">
         <v>2025</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H25" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="40">
+      <c r="H25" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="47">
         <v>0</v>
       </c>
       <c r="J25" s="5">
@@ -7100,26 +7168,26 @@
       <c r="A26" s="1">
         <v>3</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="40">
+      <c r="D26" s="47">
         <v>411</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="47">
         <v>330</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="48">
         <v>2025</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="47">
         <v>81</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="47">
         <v>411</v>
       </c>
       <c r="J26" s="5">
@@ -7172,26 +7240,26 @@
       <c r="A27" s="1">
         <v>3</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="40">
+      <c r="D27" s="47">
         <v>411</v>
       </c>
-      <c r="E27" s="40">
-        <v>362</v>
-      </c>
-      <c r="F27" s="41">
+      <c r="E27" s="47">
+        <v>330</v>
+      </c>
+      <c r="F27" s="48">
         <v>2025</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="47">
         <v>49</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="47">
         <v>411</v>
       </c>
       <c r="J27" s="5">
@@ -7244,26 +7312,26 @@
       <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="40">
+      <c r="D28" s="47">
         <v>411</v>
       </c>
-      <c r="E28" s="40">
-        <v>328</v>
-      </c>
-      <c r="F28" s="41">
+      <c r="E28" s="47">
+        <v>330</v>
+      </c>
+      <c r="F28" s="48">
         <v>2025</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="47">
         <v>83</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="47">
         <v>411</v>
       </c>
       <c r="J28" s="5">
@@ -7316,26 +7384,26 @@
       <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="40">
+      <c r="D29" s="47">
         <v>411</v>
       </c>
-      <c r="E29" s="40">
-        <v>299</v>
-      </c>
-      <c r="F29" s="41">
+      <c r="E29" s="47">
+        <v>330</v>
+      </c>
+      <c r="F29" s="48">
         <v>2025</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="47">
         <v>112</v>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="47">
         <v>411</v>
       </c>
       <c r="J29" s="5">
@@ -7388,26 +7456,26 @@
       <c r="A30" s="1">
         <v>3</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="D30" s="40">
+      <c r="D30" s="47">
         <v>411</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="47">
         <v>330</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="48">
         <v>2025</v>
       </c>
-      <c r="G30" s="40" t="s">
+      <c r="G30" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="47">
         <v>111</v>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="47">
         <v>411</v>
       </c>
       <c r="J30" s="5">
@@ -7460,26 +7528,26 @@
       <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="40">
+      <c r="D31" s="47">
         <v>411</v>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="47">
         <v>300</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="48">
         <v>2025</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="47">
         <v>111</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="47">
         <v>411</v>
       </c>
       <c r="J31" s="5">
@@ -7529,33 +7597,42 @@
       </c>
     </row>
     <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D32" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H32" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="42" t="s">
+      <c r="A32" s="45"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="49" t="s">
         <v>62</v>
       </c>
       <c r="J32" s="13"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="45"/>
       <c r="S32" s="5"/>
       <c r="T32" s="13"/>
       <c r="U32" s="13"/>
       <c r="V32" s="13"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
@@ -7564,26 +7641,26 @@
       <c r="A33" s="1">
         <v>4</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="1"/>
-      <c r="D33" s="40">
+      <c r="D33" s="47">
         <v>436</v>
       </c>
-      <c r="E33" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H33" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I33" s="40">
+      <c r="E33" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" s="47">
         <v>0</v>
       </c>
       <c r="J33" s="5">
@@ -7636,26 +7713,26 @@
       <c r="A34" s="1">
         <v>4</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="D34" s="40">
+      <c r="D34" s="47">
         <v>436</v>
       </c>
-      <c r="E34" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I34" s="40">
+      <c r="E34" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I34" s="47">
         <v>0</v>
       </c>
       <c r="J34" s="5">
@@ -7708,26 +7785,26 @@
       <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="40">
+      <c r="D35" s="47">
         <v>436</v>
       </c>
-      <c r="E35" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H35" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="40">
+      <c r="E35" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I35" s="47">
         <v>0</v>
       </c>
       <c r="J35" s="5">
@@ -7780,26 +7857,26 @@
       <c r="A36" s="1">
         <v>4</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="40">
+      <c r="D36" s="47">
         <v>436</v>
       </c>
-      <c r="E36" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="40">
+      <c r="E36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="47">
         <v>0</v>
       </c>
       <c r="J36" s="5">
@@ -7852,26 +7929,26 @@
       <c r="A37" s="1">
         <v>4</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="40">
+      <c r="D37" s="47">
         <v>436</v>
       </c>
-      <c r="E37" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I37" s="40">
+      <c r="E37" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I37" s="47">
         <v>0</v>
       </c>
       <c r="J37" s="5">
@@ -7924,26 +8001,26 @@
       <c r="A38" s="1">
         <v>4</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="40">
+      <c r="D38" s="47">
         <v>436</v>
       </c>
-      <c r="E38" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="40">
+      <c r="E38" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I38" s="47">
         <v>0</v>
       </c>
       <c r="J38" s="5">
@@ -7996,26 +8073,26 @@
       <c r="A39" s="1">
         <v>4</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="40">
+      <c r="D39" s="47">
         <v>436</v>
       </c>
-      <c r="E39" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H39" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I39" s="40">
+      <c r="E39" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I39" s="47">
         <v>0</v>
       </c>
       <c r="J39" s="5">
@@ -8068,26 +8145,26 @@
       <c r="A40" s="1">
         <v>4</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="40">
+      <c r="D40" s="47">
         <v>436</v>
       </c>
-      <c r="E40" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H40" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I40" s="40">
+      <c r="E40" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I40" s="47">
         <v>0</v>
       </c>
       <c r="J40" s="5">
@@ -8140,26 +8217,26 @@
       <c r="A41" s="1">
         <v>4</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="40">
+      <c r="D41" s="47">
         <v>436</v>
       </c>
-      <c r="E41" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H41" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I41" s="40">
+      <c r="E41" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I41" s="47">
         <v>0</v>
       </c>
       <c r="J41" s="5">
@@ -8209,33 +8286,42 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D42" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H42" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I42" s="42" t="s">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" s="49" t="s">
         <v>62</v>
       </c>
       <c r="J42" s="13"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="45"/>
       <c r="S42" s="5"/>
       <c r="T42" s="13"/>
       <c r="U42" s="13"/>
       <c r="V42" s="13"/>
+      <c r="W42" s="45"/>
+      <c r="X42" s="45"/>
       <c r="Y42" s="5"/>
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
@@ -8244,26 +8330,26 @@
       <c r="A43" s="1">
         <v>5</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="D43" s="40">
+      <c r="D43" s="47">
         <v>364</v>
       </c>
-      <c r="E43" s="40">
-        <v>360</v>
-      </c>
-      <c r="F43" s="41">
+      <c r="E43" s="47">
+        <v>191</v>
+      </c>
+      <c r="F43" s="48">
         <v>2025</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="47">
         <v>4</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="47">
         <v>364</v>
       </c>
       <c r="J43" s="5">
@@ -8316,26 +8402,26 @@
       <c r="A44" s="1">
         <v>5</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="1"/>
-      <c r="D44" s="40">
+      <c r="D44" s="47">
         <v>364</v>
       </c>
-      <c r="E44" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H44" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I44" s="40">
+      <c r="E44" s="47">
+        <v>191</v>
+      </c>
+      <c r="F44" s="48">
+        <v>2025</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" s="47">
         <v>0</v>
       </c>
       <c r="J44" s="5">
@@ -8388,26 +8474,26 @@
       <c r="A45" s="1">
         <v>5</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="1"/>
-      <c r="D45" s="40">
+      <c r="D45" s="47">
         <v>364</v>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="47">
         <v>360</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="48">
         <v>2025</v>
       </c>
-      <c r="G45" s="40" t="s">
+      <c r="G45" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H45" s="40">
+      <c r="H45" s="47">
         <v>4</v>
       </c>
-      <c r="I45" s="40">
+      <c r="I45" s="47">
         <v>364</v>
       </c>
       <c r="J45" s="5">
@@ -8460,26 +8546,26 @@
       <c r="A46" s="1">
         <v>5</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="D46" s="40">
+      <c r="D46" s="47">
         <v>364</v>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="47">
         <v>191</v>
       </c>
-      <c r="F46" s="41">
+      <c r="F46" s="48">
         <v>2025</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H46" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I46" s="40">
+      <c r="H46" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" s="47">
         <v>0</v>
       </c>
       <c r="J46" s="5">
@@ -8532,26 +8618,26 @@
       <c r="A47" s="1">
         <v>5</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="1"/>
-      <c r="D47" s="40">
+      <c r="D47" s="47">
         <v>364</v>
       </c>
-      <c r="E47" s="40">
-        <v>188</v>
-      </c>
-      <c r="F47" s="41">
+      <c r="E47" s="47">
+        <v>191</v>
+      </c>
+      <c r="F47" s="48">
         <v>2025</v>
       </c>
-      <c r="G47" s="40" t="s">
+      <c r="G47" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="40">
+      <c r="H47" s="47">
         <v>176</v>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="47">
         <v>188</v>
       </c>
       <c r="J47" s="5">
@@ -8604,26 +8690,26 @@
       <c r="A48" s="1">
         <v>5</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C48" s="1"/>
-      <c r="D48" s="40">
+      <c r="D48" s="47">
         <v>364</v>
       </c>
-      <c r="E48" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H48" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I48" s="40">
+      <c r="E48" s="47">
+        <v>191</v>
+      </c>
+      <c r="F48" s="48">
+        <v>2025</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I48" s="47">
         <v>0</v>
       </c>
       <c r="J48" s="5">
@@ -8676,26 +8762,26 @@
       <c r="A49" s="1">
         <v>5</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="1"/>
-      <c r="D49" s="40">
+      <c r="D49" s="47">
         <v>364</v>
       </c>
-      <c r="E49" s="40">
-        <v>88</v>
-      </c>
-      <c r="F49" s="41">
+      <c r="E49" s="47">
+        <v>191</v>
+      </c>
+      <c r="F49" s="48">
         <v>2025</v>
       </c>
-      <c r="G49" s="40" t="s">
+      <c r="G49" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="40">
+      <c r="H49" s="47">
         <v>276</v>
       </c>
-      <c r="I49" s="40">
+      <c r="I49" s="47">
         <v>364</v>
       </c>
       <c r="J49" s="5">
@@ -8748,26 +8834,26 @@
       <c r="A50" s="1">
         <v>5</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="1"/>
-      <c r="D50" s="40">
+      <c r="D50" s="47">
         <v>364</v>
       </c>
-      <c r="E50" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G50" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H50" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I50" s="40">
+      <c r="E50" s="47">
+        <v>191</v>
+      </c>
+      <c r="F50" s="48">
+        <v>2025</v>
+      </c>
+      <c r="G50" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" s="47">
         <v>0</v>
       </c>
       <c r="J50" s="5">
@@ -8820,26 +8906,26 @@
       <c r="A51" s="1">
         <v>5</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="1"/>
-      <c r="D51" s="40">
+      <c r="D51" s="47">
         <v>364</v>
       </c>
-      <c r="E51" s="40">
-        <v>91</v>
-      </c>
-      <c r="F51" s="41">
+      <c r="E51" s="47">
+        <v>191</v>
+      </c>
+      <c r="F51" s="48">
         <v>2025</v>
       </c>
-      <c r="G51" s="40" t="s">
+      <c r="G51" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H51" s="40">
+      <c r="H51" s="47">
         <v>273</v>
       </c>
-      <c r="I51" s="40">
+      <c r="I51" s="47">
         <v>364</v>
       </c>
       <c r="J51" s="5">
@@ -8889,33 +8975,42 @@
       </c>
     </row>
     <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D52" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F52" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G52" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H52" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I52" s="42" t="s">
+      <c r="A52" s="45"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G52" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H52" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I52" s="49" t="s">
         <v>62</v>
       </c>
       <c r="J52" s="13"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="45"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
+      <c r="Q52" s="45"/>
+      <c r="R52" s="45"/>
       <c r="S52" s="5"/>
       <c r="T52" s="13"/>
       <c r="U52" s="13"/>
       <c r="V52" s="13"/>
+      <c r="W52" s="45"/>
+      <c r="X52" s="45"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
@@ -8924,26 +9019,26 @@
       <c r="A53" s="1">
         <v>6</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="1"/>
-      <c r="D53" s="40">
+      <c r="D53" s="47">
         <v>401</v>
       </c>
-      <c r="E53" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H53" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I53" s="40">
+      <c r="E53" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G53" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H53" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I53" s="47">
         <v>0</v>
       </c>
       <c r="J53" s="5">
@@ -8996,26 +9091,26 @@
       <c r="A54" s="1">
         <v>6</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="1"/>
-      <c r="D54" s="40">
+      <c r="D54" s="47">
         <v>401</v>
       </c>
-      <c r="E54" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G54" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H54" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="40">
+      <c r="E54" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G54" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H54" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I54" s="47">
         <v>0</v>
       </c>
       <c r="J54" s="5">
@@ -9068,26 +9163,26 @@
       <c r="A55" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="1"/>
-      <c r="D55" s="40">
+      <c r="D55" s="47">
         <v>401</v>
       </c>
-      <c r="E55" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G55" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H55" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I55" s="40">
+      <c r="E55" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F55" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G55" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I55" s="47">
         <v>0</v>
       </c>
       <c r="J55" s="5">
@@ -9140,26 +9235,26 @@
       <c r="A56" s="1">
         <v>6</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="1"/>
-      <c r="D56" s="40">
+      <c r="D56" s="47">
         <v>401</v>
       </c>
-      <c r="E56" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G56" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H56" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I56" s="40">
+      <c r="E56" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F56" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G56" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H56" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I56" s="47">
         <v>0</v>
       </c>
       <c r="J56" s="5">
@@ -9212,26 +9307,26 @@
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="1"/>
-      <c r="D57" s="40">
+      <c r="D57" s="47">
         <v>401</v>
       </c>
-      <c r="E57" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F57" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G57" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H57" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I57" s="40">
+      <c r="E57" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H57" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I57" s="47">
         <v>0</v>
       </c>
       <c r="J57" s="5">
@@ -9284,26 +9379,26 @@
       <c r="A58" s="1">
         <v>6</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="1"/>
-      <c r="D58" s="40">
+      <c r="D58" s="47">
         <v>401</v>
       </c>
-      <c r="E58" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G58" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H58" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="40">
+      <c r="E58" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H58" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="47">
         <v>0</v>
       </c>
       <c r="J58" s="5">
@@ -9356,26 +9451,26 @@
       <c r="A59" s="1">
         <v>6</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="1"/>
-      <c r="D59" s="40">
+      <c r="D59" s="47">
         <v>401</v>
       </c>
-      <c r="E59" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F59" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G59" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I59" s="40">
+      <c r="E59" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G59" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H59" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" s="47">
         <v>0</v>
       </c>
       <c r="J59" s="5">
@@ -9428,26 +9523,26 @@
       <c r="A60" s="1">
         <v>6</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="1"/>
-      <c r="D60" s="40">
+      <c r="D60" s="47">
         <v>401</v>
       </c>
-      <c r="E60" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G60" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H60" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I60" s="40">
+      <c r="E60" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H60" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I60" s="47">
         <v>0</v>
       </c>
       <c r="J60" s="5">
@@ -9500,26 +9595,26 @@
       <c r="A61" s="1">
         <v>6</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="1"/>
-      <c r="D61" s="40">
+      <c r="D61" s="47">
         <v>401</v>
       </c>
-      <c r="E61" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F61" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G61" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H61" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="40">
+      <c r="E61" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H61" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" s="47">
         <v>0</v>
       </c>
       <c r="J61" s="5">
@@ -9568,25 +9663,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A62" s="45"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="45"/>
       <c r="J62" s="13"/>
+      <c r="K62" s="45"/>
+      <c r="L62" s="45"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
       <c r="P62" s="13"/>
+      <c r="Q62" s="45"/>
+      <c r="R62" s="45"/>
       <c r="S62" s="5"/>
       <c r="T62" s="13"/>
       <c r="U62" s="13"/>
       <c r="V62" s="13"/>
+      <c r="W62" s="45"/>
+      <c r="X62" s="45"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C63" s="10"/>
@@ -9651,11 +9761,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C64" s="10"/>
@@ -9720,11 +9830,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="10"/>
@@ -9789,11 +9899,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C66" s="10"/>
@@ -9858,11 +9968,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="50" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="10"/>
@@ -9927,11 +10037,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="10"/>
@@ -9996,11 +10106,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="10"/>
@@ -10065,11 +10175,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="10"/>
@@ -10134,11 +10244,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="10"/>
@@ -10203,25 +10313,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A72" s="45"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="45"/>
       <c r="J72" s="13"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="45"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
       <c r="O72" s="13"/>
       <c r="P72" s="13"/>
+      <c r="Q72" s="45"/>
+      <c r="R72" s="45"/>
       <c r="S72" s="5"/>
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="13"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
       <c r="Y72" s="5"/>
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="10"/>
@@ -10286,11 +10411,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="10"/>
@@ -10355,11 +10480,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="10"/>
@@ -10424,11 +10549,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C76" s="10"/>
@@ -10493,11 +10618,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C77" s="10"/>
@@ -10562,11 +10687,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C78" s="10"/>
@@ -10631,11 +10756,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C79" s="10"/>
@@ -10700,11 +10825,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="10"/>
@@ -10769,11 +10894,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C81" s="10"/>
@@ -10838,25 +10963,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A82" s="45"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45"/>
       <c r="J82" s="13"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
       <c r="O82" s="13"/>
       <c r="P82" s="13"/>
+      <c r="Q82" s="45"/>
+      <c r="R82" s="45"/>
       <c r="S82" s="5"/>
       <c r="T82" s="13"/>
       <c r="U82" s="13"/>
       <c r="V82" s="13"/>
+      <c r="W82" s="45"/>
+      <c r="X82" s="45"/>
       <c r="Y82" s="5"/>
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C83" s="10"/>
@@ -10921,11 +11061,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="10"/>
@@ -10990,11 +11130,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C85" s="10"/>
@@ -11059,11 +11199,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C86" s="10"/>
@@ -11128,11 +11268,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C87" s="10"/>
@@ -11197,11 +11337,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C88" s="10"/>
@@ -11266,11 +11406,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C89" s="10"/>
@@ -11335,11 +11475,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C90" s="10"/>
@@ -11404,11 +11544,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="10"/>
@@ -11473,25 +11613,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A92" s="45"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="45"/>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45"/>
+      <c r="I92" s="45"/>
       <c r="J92" s="13"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="45"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
+      <c r="Q92" s="45"/>
+      <c r="R92" s="45"/>
       <c r="S92" s="5"/>
       <c r="T92" s="13"/>
       <c r="U92" s="13"/>
       <c r="V92" s="13"/>
+      <c r="W92" s="45"/>
+      <c r="X92" s="45"/>
       <c r="Y92" s="5"/>
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C93" s="10"/>
@@ -11556,11 +11711,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="10"/>
@@ -11625,11 +11780,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="10"/>
@@ -11694,11 +11849,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C96" s="10"/>
@@ -11763,11 +11918,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C97" s="10"/>
@@ -11832,11 +11987,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C98" s="10"/>
@@ -11901,11 +12056,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C99" s="10"/>
@@ -11970,11 +12125,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C100" s="10"/>
@@ -12039,11 +12194,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C101" s="10"/>
@@ -12108,25 +12263,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A102" s="45"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="45"/>
+      <c r="D102" s="45"/>
+      <c r="E102" s="45"/>
+      <c r="F102" s="45"/>
+      <c r="G102" s="45"/>
+      <c r="H102" s="45"/>
+      <c r="I102" s="45"/>
       <c r="J102" s="13"/>
+      <c r="K102" s="45"/>
+      <c r="L102" s="45"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
       <c r="O102" s="13"/>
       <c r="P102" s="13"/>
+      <c r="Q102" s="45"/>
+      <c r="R102" s="45"/>
       <c r="S102" s="5"/>
       <c r="T102" s="13"/>
       <c r="U102" s="13"/>
       <c r="V102" s="13"/>
+      <c r="W102" s="45"/>
+      <c r="X102" s="45"/>
       <c r="Y102" s="5"/>
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C103" s="1"/>
@@ -12191,11 +12361,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="46" t="s">
         <v>25</v>
       </c>
       <c r="C104" s="1"/>
@@ -12260,11 +12430,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="46" t="s">
         <v>26</v>
       </c>
       <c r="C105" s="1"/>
@@ -12329,11 +12499,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="46" t="s">
         <v>27</v>
       </c>
       <c r="C106" s="1"/>
@@ -12398,11 +12568,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="46" t="s">
         <v>28</v>
       </c>
       <c r="C107" s="1"/>
@@ -12467,11 +12637,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="46" t="s">
         <v>29</v>
       </c>
       <c r="C108" s="1"/>
@@ -12536,11 +12706,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="46" t="s">
         <v>30</v>
       </c>
       <c r="C109" s="1"/>
@@ -12605,11 +12775,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="46" t="s">
         <v>31</v>
       </c>
       <c r="C110" s="1"/>
@@ -12674,20 +12844,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="A111" s="45"/>
+      <c r="B111" s="45"/>
+      <c r="C111" s="45"/>
+      <c r="D111" s="45"/>
+      <c r="E111" s="45"/>
+      <c r="F111" s="45"/>
+      <c r="G111" s="45"/>
+      <c r="H111" s="45"/>
+      <c r="I111" s="45"/>
       <c r="J111" s="13"/>
+      <c r="K111" s="45"/>
+      <c r="L111" s="45"/>
+      <c r="M111" s="45"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
       <c r="P111" s="13"/>
+      <c r="Q111" s="45"/>
+      <c r="R111" s="45"/>
+      <c r="S111" s="45"/>
       <c r="T111" s="13"/>
       <c r="U111" s="13"/>
       <c r="V111" s="13"/>
+      <c r="W111" s="45"/>
+      <c r="X111" s="45"/>
+      <c r="Y111" s="45"/>
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
-      <c r="B112" s="9"/>
+      <c r="B112" s="46"/>
       <c r="C112" s="1"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
@@ -12747,9 +12935,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
-      <c r="B113" s="9"/>
+      <c r="B113" s="46"/>
       <c r="C113" s="1"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
@@ -12809,9 +12997,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
-      <c r="B114" s="9"/>
+      <c r="B114" s="46"/>
       <c r="C114" s="1"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
@@ -12871,9 +13059,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
-      <c r="B115" s="9"/>
+      <c r="B115" s="46"/>
       <c r="C115" s="1"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
@@ -12933,9 +13121,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
-      <c r="B116" s="9"/>
+      <c r="B116" s="46"/>
       <c r="C116" s="1"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
@@ -12995,9 +13183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
-      <c r="B117" s="9"/>
+      <c r="B117" s="46"/>
       <c r="C117" s="1"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
@@ -13057,9 +13245,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
-      <c r="B118" s="9"/>
+      <c r="B118" s="46"/>
       <c r="C118" s="1"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
@@ -13119,9 +13307,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
-      <c r="B119" s="9"/>
+      <c r="B119" s="46"/>
       <c r="C119" s="1"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
@@ -13181,9 +13369,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
-      <c r="B120" s="9"/>
+      <c r="B120" s="46"/>
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
@@ -13243,9 +13431,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
-      <c r="B121" s="9"/>
+      <c r="B121" s="46"/>
       <c r="C121" s="1"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
@@ -13305,9 +13493,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
-      <c r="B122" s="9"/>
+      <c r="B122" s="46"/>
       <c r="C122" s="1"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
@@ -13367,9 +13555,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
-      <c r="B123" s="9"/>
+      <c r="B123" s="46"/>
       <c r="C123" s="1"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
@@ -13429,9 +13617,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
-      <c r="B124" s="9"/>
+      <c r="B124" s="46"/>
       <c r="C124" s="1"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
@@ -13491,9 +13679,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
-      <c r="B125" s="9"/>
+      <c r="B125" s="46"/>
       <c r="C125" s="1"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
@@ -13553,9 +13741,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
-      <c r="B126" s="9"/>
+      <c r="B126" s="46"/>
       <c r="C126" s="1"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
@@ -13615,14 +13803,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
-      <c r="B127" s="30"/>
+      <c r="B127" s="51"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
-      <c r="E127" s="31"/>
+      <c r="E127" s="30"/>
       <c r="F127" s="29"/>
-      <c r="G127" s="31"/>
+      <c r="G127" s="30"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
         <v>0</v>
@@ -13635,9 +13823,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K127" s="31"/>
+      <c r="K127" s="30"/>
       <c r="L127" s="29"/>
-      <c r="M127" s="31"/>
+      <c r="M127" s="30"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
@@ -13647,9 +13835,9 @@
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
-      <c r="Q127" s="31"/>
+      <c r="Q127" s="30"/>
       <c r="R127" s="29"/>
-      <c r="S127" s="31"/>
+      <c r="S127" s="30"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -13662,9 +13850,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W127" s="31"/>
+      <c r="W127" s="30"/>
       <c r="X127" s="29"/>
-      <c r="Y127" s="31"/>
+      <c r="Y127" s="30"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -13674,190 +13862,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 D23:F31 K14:L21 D43:F51" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 M3 Y14:Y110 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G14:G21 G23:G31 M14:M110 G43:G51" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13870,11 +13878,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 X112:X127 F103:F110 R103:R110 F63:F71 F73:F81 L103:L110 X103:X110 F83:F91 F93:F101" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G93:G101 Y14:Y110 S4:S110 G103:G110 M5:M12 Y5:Y12 G63:G71 G73:G81 G83:G91 M14:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+      <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G103:G110 M5:M12 Y5:Y12 G63:G71 G73:G81 G83:G91 G93:G101" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
-      <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{42DD6D97-B829-4A49-A0CA-DD668E00D054}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13889,11 +13897,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" style="57" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
     <col min="5" max="5" width="23.140625" customWidth="1"/>
@@ -13918,45 +13926,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="B1" s="35"/>
-      <c r="D1" s="51" t="s">
+      <c r="B1" s="58"/>
+      <c r="D1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="52" t="s">
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="53" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="54" t="s">
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
@@ -13989,10 +13997,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="37" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -14025,10 +14033,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="48" t="s">
+      <c r="Y2" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="48" t="s">
+      <c r="Z2" s="38" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14039,26 +14047,26 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="40">
+      <c r="D3" s="47">
         <v>341</v>
       </c>
-      <c r="E3" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="40">
+      <c r="E3" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="47">
         <v>0</v>
       </c>
       <c r="J3" s="5">
@@ -14111,26 +14119,26 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="40">
+      <c r="D4" s="47">
         <v>341</v>
       </c>
-      <c r="E4" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="40">
+      <c r="E4" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="47">
         <v>0</v>
       </c>
       <c r="J4" s="5">
@@ -14183,26 +14191,26 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="40">
+      <c r="D5" s="47">
         <v>341</v>
       </c>
-      <c r="E5" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="40">
+      <c r="E5" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="47">
         <v>0</v>
       </c>
       <c r="J5" s="5">
@@ -14255,26 +14263,26 @@
       <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="40">
+      <c r="D6" s="47">
         <v>341</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="40">
+      <c r="E6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="47">
         <v>0</v>
       </c>
       <c r="J6" s="5">
@@ -14327,26 +14335,26 @@
       <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="40">
+      <c r="D7" s="47">
         <v>341</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="40">
+      <c r="E7" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="47">
         <v>0</v>
       </c>
       <c r="J7" s="5">
@@ -14399,26 +14407,26 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="40">
+      <c r="D8" s="47">
         <v>341</v>
       </c>
-      <c r="E8" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="40">
+      <c r="E8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="47">
         <v>0</v>
       </c>
       <c r="J8" s="5">
@@ -14471,26 +14479,26 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="40">
+      <c r="D9" s="47">
         <v>341</v>
       </c>
-      <c r="E9" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="40">
+      <c r="E9" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="47">
         <v>0</v>
       </c>
       <c r="J9" s="5">
@@ -14543,26 +14551,26 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="40">
+      <c r="D10" s="47">
         <v>341</v>
       </c>
-      <c r="E10" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="40">
+      <c r="E10" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="47">
         <v>0</v>
       </c>
       <c r="J10" s="5">
@@ -14612,49 +14620,70 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1" ht="15">
-      <c r="D11" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="42" t="s">
-        <v>62</v>
-      </c>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="45"/>
     </row>
     <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="40">
+      <c r="D12" s="47">
         <v>379</v>
       </c>
-      <c r="E12" s="40">
-        <v>0</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="40">
+      <c r="E12" s="47">
+        <v>0</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="47">
         <v>0</v>
       </c>
       <c r="J12" s="5">
@@ -14707,26 +14736,26 @@
       <c r="A13" s="1">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="40">
+      <c r="D13" s="47">
         <v>379</v>
       </c>
-      <c r="E13" s="40">
-        <v>0</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="40">
+      <c r="E13" s="47">
+        <v>0</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="47">
         <v>0</v>
       </c>
       <c r="J13" s="5">
@@ -14779,26 +14808,26 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="40">
+      <c r="D14" s="47">
         <v>379</v>
       </c>
-      <c r="E14" s="40">
-        <v>0</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="40">
+      <c r="E14" s="47">
+        <v>0</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="47">
         <v>0</v>
       </c>
       <c r="J14" s="5">
@@ -14851,26 +14880,26 @@
       <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="40">
+      <c r="D15" s="47">
         <v>379</v>
       </c>
-      <c r="E15" s="40">
-        <v>0</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="40">
+      <c r="E15" s="47">
+        <v>0</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="47">
         <v>0</v>
       </c>
       <c r="J15" s="5">
@@ -14923,26 +14952,26 @@
       <c r="A16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="40">
+      <c r="D16" s="47">
         <v>379</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="47">
         <v>300</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="48">
         <v>2024</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="40">
+      <c r="H16" s="47">
         <v>79</v>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="47">
         <v>379</v>
       </c>
       <c r="J16" s="5">
@@ -15001,26 +15030,26 @@
       <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="40">
+      <c r="D17" s="47">
         <v>379</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="47">
         <v>300</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="48">
         <v>2024</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="47">
         <v>79</v>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="47">
         <v>379</v>
       </c>
       <c r="J17" s="5">
@@ -15079,26 +15108,26 @@
       <c r="A18" s="1">
         <v>2</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="40">
+      <c r="D18" s="47">
         <v>379</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="47">
         <v>300</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="48">
         <v>2024</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="47">
         <v>79</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="47">
         <v>379</v>
       </c>
       <c r="J18" s="5">
@@ -15157,26 +15186,26 @@
       <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="40">
+      <c r="D19" s="47">
         <v>379</v>
       </c>
-      <c r="E19" s="40">
-        <v>0</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="40">
+      <c r="E19" s="47">
+        <v>0</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="47">
         <v>0</v>
       </c>
       <c r="J19" s="5">
@@ -15226,50 +15255,68 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="D20" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="46"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="55"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45"/>
+      <c r="T20" s="45"/>
+      <c r="U20" s="45"/>
+      <c r="V20" s="45"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="56"/>
+      <c r="Y20" s="56"/>
+      <c r="Z20" s="45"/>
+      <c r="AA20" s="45"/>
     </row>
     <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="46" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="40">
+      <c r="D21" s="47">
         <v>411</v>
       </c>
-      <c r="E21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="40">
+      <c r="E21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="47">
         <v>0</v>
       </c>
       <c r="J21" s="5">
@@ -15322,26 +15369,26 @@
       <c r="A22" s="1">
         <v>3</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="40">
+      <c r="D22" s="47">
         <v>411</v>
       </c>
-      <c r="E22" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="40">
+      <c r="E22" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="47">
         <v>0</v>
       </c>
       <c r="J22" s="5">
@@ -15394,26 +15441,26 @@
       <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="40">
+      <c r="D23" s="47">
         <v>411</v>
       </c>
-      <c r="E23" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="40">
+      <c r="E23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="47">
         <v>0</v>
       </c>
       <c r="J23" s="5">
@@ -15466,26 +15513,26 @@
       <c r="A24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="40">
+      <c r="D24" s="47">
         <v>411</v>
       </c>
-      <c r="E24" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="40">
+      <c r="E24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="47">
         <v>0</v>
       </c>
       <c r="J24" s="5">
@@ -15538,26 +15585,26 @@
       <c r="A25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="1"/>
-      <c r="D25" s="40">
+      <c r="D25" s="47">
         <v>411</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="40">
+      <c r="E25" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="47">
         <v>0</v>
       </c>
       <c r="J25" s="5">
@@ -15610,26 +15657,26 @@
       <c r="A26" s="1">
         <v>3</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="40">
+      <c r="D26" s="47">
         <v>411</v>
       </c>
-      <c r="E26" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" s="40">
+      <c r="E26" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="47">
         <v>0</v>
       </c>
       <c r="J26" s="5">
@@ -15688,26 +15735,26 @@
       <c r="A27" s="1">
         <v>3</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="40">
+      <c r="D27" s="47">
         <v>411</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="47">
         <v>250</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="48">
         <v>2024</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="47">
         <v>161</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="47">
         <v>411</v>
       </c>
       <c r="J27" s="5">
@@ -15760,26 +15807,26 @@
       <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="40">
+      <c r="D28" s="47">
         <v>411</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="47">
         <v>250</v>
       </c>
-      <c r="F28" s="41">
+      <c r="F28" s="48">
         <v>2024</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="47">
         <v>161</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="47">
         <v>411</v>
       </c>
       <c r="J28" s="5">
@@ -15838,26 +15885,26 @@
       <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="46" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="40">
+      <c r="D29" s="47">
         <v>411</v>
       </c>
-      <c r="E29" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" s="40">
+      <c r="E29" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="47">
         <v>411</v>
       </c>
       <c r="J29" s="5">
@@ -15906,31 +15953,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="45"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
+      <c r="X30" s="45"/>
+      <c r="Y30" s="45"/>
+      <c r="Z30" s="45"/>
+      <c r="AA30" s="45"/>
+    </row>
     <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="40">
+      <c r="D31" s="47">
         <v>436</v>
       </c>
-      <c r="E31" s="40">
-        <v>0</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="40">
+      <c r="E31" s="47">
+        <v>0</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="47">
         <v>0</v>
       </c>
       <c r="J31" s="5">
@@ -15983,26 +16058,26 @@
       <c r="A32" s="1">
         <v>4</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="1"/>
-      <c r="D32" s="40">
+      <c r="D32" s="47">
         <v>436</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="47">
         <v>200</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="48">
         <v>2024</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="47">
         <v>236</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="47">
         <v>436</v>
       </c>
       <c r="J32" s="5">
@@ -16055,26 +16130,26 @@
       <c r="A33" s="1">
         <v>4</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1"/>
-      <c r="D33" s="40">
+      <c r="D33" s="47">
         <v>436</v>
       </c>
-      <c r="E33" s="40">
+      <c r="E33" s="47">
         <v>200</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="48">
         <v>2024</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="G33" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="47">
         <v>236</v>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="47">
         <v>436</v>
       </c>
       <c r="J33" s="5">
@@ -16127,26 +16202,26 @@
       <c r="A34" s="1">
         <v>4</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="D34" s="40">
+      <c r="D34" s="47">
         <v>436</v>
       </c>
-      <c r="E34" s="40">
-        <v>0</v>
-      </c>
-      <c r="F34" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I34" s="40">
+      <c r="E34" s="47">
+        <v>0</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I34" s="47">
         <v>0</v>
       </c>
       <c r="J34" s="5">
@@ -16199,26 +16274,26 @@
       <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="40">
+      <c r="D35" s="47">
         <v>436</v>
       </c>
-      <c r="E35" s="40">
+      <c r="E35" s="47">
         <v>300</v>
       </c>
-      <c r="F35" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35" s="40" t="s">
+      <c r="F35" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H35" s="40">
+      <c r="H35" s="47">
         <v>136</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="47">
         <v>0</v>
       </c>
       <c r="J35" s="5">
@@ -16271,26 +16346,26 @@
       <c r="A36" s="1">
         <v>4</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="40">
+      <c r="D36" s="47">
         <v>436</v>
       </c>
-      <c r="E36" s="40">
-        <v>0</v>
-      </c>
-      <c r="F36" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="40">
+      <c r="E36" s="47">
+        <v>0</v>
+      </c>
+      <c r="F36" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="47">
         <v>0</v>
       </c>
       <c r="J36" s="5">
@@ -16340,29 +16415,29 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="19.5">
-      <c r="A37" s="37">
+      <c r="A37" s="34">
         <v>4</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="46" t="s">
         <v>88</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="40">
+      <c r="D37" s="47">
         <v>436</v>
       </c>
-      <c r="E37" s="40">
-        <v>0</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I37" s="40">
+      <c r="E37" s="47">
+        <v>0</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I37" s="47">
         <v>0</v>
       </c>
       <c r="J37" s="5">
@@ -16415,26 +16490,26 @@
       <c r="A38" s="1">
         <v>4</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="46" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="40">
+      <c r="D38" s="47">
         <v>436</v>
       </c>
-      <c r="E38" s="40">
-        <v>0</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="40">
+      <c r="E38" s="47">
+        <v>0</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I38" s="47">
         <v>0</v>
       </c>
       <c r="J38" s="5">
@@ -16487,26 +16562,26 @@
       <c r="A39" s="1">
         <v>4</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="40">
+      <c r="D39" s="47">
         <v>436</v>
       </c>
-      <c r="E39" s="40">
-        <v>0</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H39" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I39" s="40">
+      <c r="E39" s="47">
+        <v>0</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I39" s="47">
         <v>0</v>
       </c>
       <c r="J39" s="5">
@@ -16556,10 +16631,10 @@
       </c>
     </row>
     <row r="40" spans="1:27" ht="19.5">
-      <c r="A40" s="37">
+      <c r="A40" s="34">
         <v>4</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="46" t="s">
         <v>90</v>
       </c>
       <c r="C40" s="5"/>
@@ -16628,7 +16703,7 @@
       <c r="A41" s="1">
         <v>4</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="46" t="s">
         <v>91</v>
       </c>
       <c r="C41" s="1"/>
@@ -16693,34 +16768,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+      <c r="O42" s="45"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="45"/>
+      <c r="S42" s="45"/>
+      <c r="T42" s="45"/>
+      <c r="U42" s="45"/>
+      <c r="V42" s="45"/>
+      <c r="W42" s="45"/>
+      <c r="X42" s="45"/>
+      <c r="Y42" s="45"/>
+      <c r="Z42" s="45"/>
+      <c r="AA42" s="45"/>
+    </row>
     <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="D43" s="40">
+      <c r="D43" s="47">
         <v>364</v>
       </c>
-      <c r="E43" s="40">
+      <c r="E43" s="47">
         <v>191</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="48">
         <v>2025</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="47">
         <v>173</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="47">
         <v>364</v>
       </c>
-      <c r="J43" s="40">
+      <c r="J43" s="47">
         <v>0</v>
       </c>
       <c r="K43" s="5"/>
@@ -16769,29 +16872,29 @@
       <c r="A44" s="1">
         <v>5</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="1"/>
-      <c r="D44" s="40">
+      <c r="D44" s="47">
         <v>364</v>
       </c>
-      <c r="E44" s="40">
+      <c r="E44" s="47">
         <v>191</v>
       </c>
-      <c r="F44" s="41">
+      <c r="F44" s="48">
         <v>2025</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H44" s="40">
+      <c r="H44" s="47">
         <v>173</v>
       </c>
-      <c r="I44" s="40">
+      <c r="I44" s="47">
         <v>364</v>
       </c>
-      <c r="J44" s="40">
+      <c r="J44" s="47">
         <v>0</v>
       </c>
       <c r="K44" s="5"/>
@@ -16840,29 +16943,29 @@
       <c r="A45" s="1">
         <v>5</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="1"/>
-      <c r="D45" s="40">
+      <c r="D45" s="47">
         <v>364</v>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="47">
         <v>191</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="48">
         <v>2025</v>
       </c>
-      <c r="G45" s="40" t="s">
+      <c r="G45" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H45" s="40">
+      <c r="H45" s="47">
         <v>173</v>
       </c>
-      <c r="I45" s="40">
+      <c r="I45" s="47">
         <v>364</v>
       </c>
-      <c r="J45" s="40">
+      <c r="J45" s="47">
         <v>0</v>
       </c>
       <c r="K45" s="5"/>
@@ -16911,29 +17014,29 @@
       <c r="A46" s="1">
         <v>5</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="D46" s="40">
+      <c r="D46" s="47">
         <v>364</v>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="47">
         <v>300</v>
       </c>
-      <c r="F46" s="41">
+      <c r="F46" s="48">
         <v>2025</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H46" s="40">
+      <c r="H46" s="47">
         <v>64</v>
       </c>
-      <c r="I46" s="40">
+      <c r="I46" s="47">
         <v>364</v>
       </c>
-      <c r="J46" s="40">
+      <c r="J46" s="47">
         <v>0</v>
       </c>
       <c r="K46" s="5"/>
@@ -16982,29 +17085,29 @@
       <c r="A47" s="1">
         <v>5</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="1"/>
-      <c r="D47" s="40">
+      <c r="D47" s="47">
         <v>364</v>
       </c>
-      <c r="E47" s="40">
-        <v>0</v>
-      </c>
-      <c r="F47" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H47" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I47" s="40">
-        <v>0</v>
-      </c>
-      <c r="J47" s="40">
+      <c r="E47" s="47">
+        <v>0</v>
+      </c>
+      <c r="F47" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I47" s="47">
+        <v>0</v>
+      </c>
+      <c r="J47" s="47">
         <v>0</v>
       </c>
       <c r="K47" s="5"/>
@@ -17053,29 +17156,29 @@
       <c r="A48" s="1">
         <v>5</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C48" s="1"/>
-      <c r="D48" s="40">
+      <c r="D48" s="47">
         <v>364</v>
       </c>
-      <c r="E48" s="40">
+      <c r="E48" s="47">
         <v>191</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F48" s="48">
         <v>2025</v>
       </c>
-      <c r="G48" s="40" t="s">
+      <c r="G48" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="40">
+      <c r="H48" s="47">
         <v>173</v>
       </c>
-      <c r="I48" s="40">
+      <c r="I48" s="47">
         <v>364</v>
       </c>
-      <c r="J48" s="40">
+      <c r="J48" s="47">
         <v>0</v>
       </c>
       <c r="K48" s="5"/>
@@ -17121,32 +17224,32 @@
       </c>
     </row>
     <row r="49" spans="1:27" ht="19.5">
-      <c r="A49" s="37">
+      <c r="A49" s="34">
         <v>5</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="46" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="40">
+      <c r="D49" s="47">
         <v>364</v>
       </c>
-      <c r="E49" s="40">
-        <v>0</v>
-      </c>
-      <c r="F49" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H49" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I49" s="40">
-        <v>0</v>
-      </c>
-      <c r="J49" s="40">
+      <c r="E49" s="47">
+        <v>0</v>
+      </c>
+      <c r="F49" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H49" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I49" s="47">
+        <v>0</v>
+      </c>
+      <c r="J49" s="47">
         <v>0</v>
       </c>
       <c r="K49" s="5"/>
@@ -17195,29 +17298,29 @@
       <c r="A50" s="1">
         <v>5</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="46" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="1"/>
-      <c r="D50" s="40">
+      <c r="D50" s="47">
         <v>364</v>
       </c>
-      <c r="E50" s="40">
+      <c r="E50" s="47">
         <v>332</v>
       </c>
-      <c r="F50" s="41">
+      <c r="F50" s="48">
         <v>2025</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H50" s="40">
+      <c r="H50" s="47">
         <v>32</v>
       </c>
-      <c r="I50" s="40">
+      <c r="I50" s="47">
         <v>364</v>
       </c>
-      <c r="J50" s="40">
+      <c r="J50" s="47">
         <v>0</v>
       </c>
       <c r="K50" s="5"/>
@@ -17266,7 +17369,7 @@
       <c r="A51" s="1">
         <v>5</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C51" s="1"/>
@@ -17331,10 +17434,10 @@
       </c>
     </row>
     <row r="52" spans="1:27" ht="19.5">
-      <c r="A52" s="37">
+      <c r="A52" s="34">
         <v>5</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="46" t="s">
         <v>90</v>
       </c>
       <c r="C52" s="5"/>
@@ -17403,7 +17506,7 @@
       <c r="A53" s="1">
         <v>5</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="46" t="s">
         <v>91</v>
       </c>
       <c r="C53" s="1"/>
@@ -17468,34 +17571,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A54" s="45"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="45"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="45"/>
+      <c r="O54" s="45"/>
+      <c r="P54" s="45"/>
+      <c r="Q54" s="45"/>
+      <c r="R54" s="45"/>
+      <c r="S54" s="45"/>
+      <c r="T54" s="45"/>
+      <c r="U54" s="45"/>
+      <c r="V54" s="45"/>
+      <c r="W54" s="45"/>
+      <c r="X54" s="45"/>
+      <c r="Y54" s="45"/>
+      <c r="Z54" s="45"/>
+      <c r="AA54" s="45"/>
+    </row>
     <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="1"/>
-      <c r="D55" s="40">
+      <c r="D55" s="47">
         <v>401</v>
       </c>
-      <c r="E55" s="40">
+      <c r="E55" s="47">
         <v>50</v>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="48">
         <v>2025</v>
       </c>
-      <c r="G55" s="40" t="s">
+      <c r="G55" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H55" s="40">
+      <c r="H55" s="47">
         <v>351</v>
       </c>
-      <c r="I55" s="40">
+      <c r="I55" s="47">
         <v>401</v>
       </c>
-      <c r="J55" s="40">
+      <c r="J55" s="47">
         <v>0</v>
       </c>
       <c r="K55" s="5">
@@ -17550,29 +17681,29 @@
       <c r="A56" s="1">
         <v>6</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="1"/>
-      <c r="D56" s="40">
+      <c r="D56" s="47">
         <v>401</v>
       </c>
-      <c r="E56" s="40">
+      <c r="E56" s="47">
         <v>50</v>
       </c>
-      <c r="F56" s="41">
+      <c r="F56" s="48">
         <v>2025</v>
       </c>
-      <c r="G56" s="40" t="s">
+      <c r="G56" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="47">
         <v>351</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="47">
         <v>401</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="47">
         <v>0</v>
       </c>
       <c r="K56" s="5">
@@ -17633,29 +17764,29 @@
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="1"/>
-      <c r="D57" s="40">
+      <c r="D57" s="47">
         <v>401</v>
       </c>
-      <c r="E57" s="40">
+      <c r="E57" s="47">
         <v>50</v>
       </c>
-      <c r="F57" s="41">
+      <c r="F57" s="48">
         <v>2025</v>
       </c>
-      <c r="G57" s="40" t="s">
+      <c r="G57" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="H57" s="40">
+      <c r="H57" s="47">
         <v>351</v>
       </c>
-      <c r="I57" s="40">
+      <c r="I57" s="47">
         <v>401</v>
       </c>
-      <c r="J57" s="40">
+      <c r="J57" s="47">
         <v>0</v>
       </c>
       <c r="K57" s="5">
@@ -17679,7 +17810,7 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="49">
+      <c r="Q57" s="39">
         <v>400</v>
       </c>
       <c r="R57" s="1">
@@ -17716,29 +17847,29 @@
       <c r="A58" s="1">
         <v>6</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="46" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="1"/>
-      <c r="D58" s="40">
+      <c r="D58" s="47">
         <v>401</v>
       </c>
-      <c r="E58" s="40">
-        <v>0</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G58" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H58" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="40">
-        <v>0</v>
-      </c>
-      <c r="J58" s="40">
+      <c r="E58" s="47">
+        <v>0</v>
+      </c>
+      <c r="F58" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H58" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="47">
+        <v>0</v>
+      </c>
+      <c r="J58" s="47">
         <v>0</v>
       </c>
       <c r="K58" s="5"/>
@@ -17787,29 +17918,29 @@
       <c r="A59" s="1">
         <v>6</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="1"/>
-      <c r="D59" s="40">
+      <c r="D59" s="47">
         <v>401</v>
       </c>
-      <c r="E59" s="40">
-        <v>0</v>
-      </c>
-      <c r="F59" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G59" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I59" s="40">
-        <v>0</v>
-      </c>
-      <c r="J59" s="40">
+      <c r="E59" s="47">
+        <v>0</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G59" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H59" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" s="47">
+        <v>0</v>
+      </c>
+      <c r="J59" s="47">
         <v>0</v>
       </c>
       <c r="K59" s="5"/>
@@ -17864,29 +17995,29 @@
       <c r="A60" s="1">
         <v>6</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="1"/>
-      <c r="D60" s="40">
+      <c r="D60" s="47">
         <v>401</v>
       </c>
-      <c r="E60" s="40">
-        <v>0</v>
-      </c>
-      <c r="F60" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G60" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H60" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I60" s="40">
-        <v>0</v>
-      </c>
-      <c r="J60" s="40">
+      <c r="E60" s="47">
+        <v>0</v>
+      </c>
+      <c r="F60" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H60" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I60" s="47">
+        <v>0</v>
+      </c>
+      <c r="J60" s="47">
         <v>0</v>
       </c>
       <c r="K60" s="5"/>
@@ -17938,32 +18069,32 @@
       </c>
     </row>
     <row r="61" spans="1:27" ht="19.5">
-      <c r="A61" s="37">
+      <c r="A61" s="34">
         <v>6</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="46" t="s">
         <v>88</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="40">
+      <c r="D61" s="47">
         <v>401</v>
       </c>
-      <c r="E61" s="40">
-        <v>0</v>
-      </c>
-      <c r="F61" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G61" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H61" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="40">
-        <v>0</v>
-      </c>
-      <c r="J61" s="40">
+      <c r="E61" s="47">
+        <v>0</v>
+      </c>
+      <c r="F61" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H61" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" s="47">
+        <v>0</v>
+      </c>
+      <c r="J61" s="47">
         <v>0</v>
       </c>
       <c r="K61" s="5"/>
@@ -18018,29 +18149,29 @@
       <c r="A62" s="1">
         <v>6</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="46" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="1"/>
-      <c r="D62" s="40">
+      <c r="D62" s="47">
         <v>401</v>
       </c>
-      <c r="E62" s="40">
-        <v>0</v>
-      </c>
-      <c r="F62" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G62" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H62" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I62" s="40">
-        <v>0</v>
-      </c>
-      <c r="J62" s="40">
+      <c r="E62" s="47">
+        <v>0</v>
+      </c>
+      <c r="F62" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" s="47">
+        <v>0</v>
+      </c>
+      <c r="J62" s="47">
         <v>0</v>
       </c>
       <c r="K62" s="5"/>
@@ -18095,29 +18226,29 @@
       <c r="A63" s="1">
         <v>6</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="1"/>
-      <c r="D63" s="40">
+      <c r="D63" s="47">
         <v>401</v>
       </c>
-      <c r="E63" s="40">
-        <v>0</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H63" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I63" s="40">
-        <v>0</v>
-      </c>
-      <c r="J63" s="40">
+      <c r="E63" s="47">
+        <v>0</v>
+      </c>
+      <c r="F63" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G63" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H63" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I63" s="47">
+        <v>0</v>
+      </c>
+      <c r="J63" s="47">
         <v>0</v>
       </c>
       <c r="K63" s="5"/>
@@ -18163,32 +18294,32 @@
       </c>
     </row>
     <row r="64" spans="1:27" ht="19.5">
-      <c r="A64" s="37">
+      <c r="A64" s="34">
         <v>6</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="46" t="s">
         <v>90</v>
       </c>
       <c r="C64" s="5"/>
-      <c r="D64" s="40">
+      <c r="D64" s="47">
         <v>401</v>
       </c>
-      <c r="E64" s="40">
-        <v>0</v>
-      </c>
-      <c r="F64" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G64" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H64" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I64" s="40">
-        <v>0</v>
-      </c>
-      <c r="J64" s="40">
+      <c r="E64" s="47">
+        <v>0</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H64" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I64" s="47">
+        <v>0</v>
+      </c>
+      <c r="J64" s="47">
         <v>0</v>
       </c>
       <c r="K64" s="5"/>
@@ -18243,29 +18374,29 @@
       <c r="A65" s="1">
         <v>6</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="46" t="s">
         <v>91</v>
       </c>
       <c r="C65" s="1"/>
-      <c r="D65" s="40">
+      <c r="D65" s="47">
         <v>401</v>
       </c>
-      <c r="E65" s="40">
-        <v>0</v>
-      </c>
-      <c r="F65" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G65" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="H65" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I65" s="40">
-        <v>0</v>
-      </c>
-      <c r="J65" s="40">
+      <c r="E65" s="47">
+        <v>0</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G65" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H65" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I65" s="47">
+        <v>0</v>
+      </c>
+      <c r="J65" s="47">
         <v>0</v>
       </c>
       <c r="K65" s="5"/>
@@ -18316,12 +18447,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1">
+      <c r="A66" s="45"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="45"/>
+      <c r="N66" s="45"/>
+      <c r="O66" s="45"/>
+      <c r="P66" s="45"/>
+      <c r="Q66" s="45"/>
+      <c r="R66" s="45"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="45"/>
+      <c r="U66" s="45"/>
+      <c r="V66" s="45"/>
+      <c r="W66" s="45"/>
+      <c r="X66" s="45"/>
+      <c r="Y66" s="45"/>
+      <c r="Z66" s="45"/>
+      <c r="AA66" s="45"/>
+    </row>
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="10"/>
@@ -18386,11 +18545,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C68" s="10"/>
@@ -18455,11 +18614,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="10"/>
@@ -18524,11 +18683,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C70" s="10"/>
@@ -18593,11 +18752,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="50" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="10"/>
@@ -18662,11 +18821,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C72" s="10"/>
@@ -18731,11 +18890,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
-      <c r="A73" s="38">
+    <row r="73" spans="1:27" ht="19.5">
+      <c r="A73" s="35">
         <v>7</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="50" t="s">
         <v>88</v>
       </c>
       <c r="C73" s="12"/>
@@ -18800,11 +18959,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="50" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="10"/>
@@ -18869,11 +19028,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="10"/>
@@ -18938,11 +19097,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
-      <c r="A76" s="38">
+    <row r="76" spans="1:27" ht="19.5">
+      <c r="A76" s="35">
         <v>7</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="50" t="s">
         <v>90</v>
       </c>
       <c r="C76" s="12"/>
@@ -19007,11 +19166,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C77" s="10"/>
@@ -19076,12 +19235,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1">
+      <c r="A78" s="45"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="45"/>
+      <c r="N78" s="45"/>
+      <c r="O78" s="45"/>
+      <c r="P78" s="45"/>
+      <c r="Q78" s="45"/>
+      <c r="R78" s="45"/>
+      <c r="S78" s="45"/>
+      <c r="T78" s="45"/>
+      <c r="U78" s="45"/>
+      <c r="V78" s="45"/>
+      <c r="W78" s="45"/>
+      <c r="X78" s="45"/>
+      <c r="Y78" s="45"/>
+      <c r="Z78" s="45"/>
+      <c r="AA78" s="45"/>
+    </row>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C79" s="10"/>
@@ -19146,11 +19333,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="10"/>
@@ -19215,11 +19402,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="10"/>
@@ -19284,11 +19471,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C82" s="10"/>
@@ -19353,11 +19540,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C83" s="10"/>
@@ -19422,11 +19609,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C84" s="10"/>
@@ -19491,11 +19678,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
-      <c r="A85" s="38">
+    <row r="85" spans="1:27" ht="19.5">
+      <c r="A85" s="35">
         <v>8</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="50" t="s">
         <v>88</v>
       </c>
       <c r="C85" s="12"/>
@@ -19560,11 +19747,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="50" t="s">
         <v>89</v>
       </c>
       <c r="C86" s="10"/>
@@ -19629,11 +19816,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C87" s="10"/>
@@ -19698,11 +19885,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
-      <c r="A88" s="38">
+    <row r="88" spans="1:27" ht="19.5">
+      <c r="A88" s="35">
         <v>8</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="50" t="s">
         <v>90</v>
       </c>
       <c r="C88" s="12"/>
@@ -19767,11 +19954,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C89" s="10"/>
@@ -19836,12 +20023,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1">
+      <c r="A90" s="45"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="45"/>
+      <c r="L90" s="45"/>
+      <c r="M90" s="45"/>
+      <c r="N90" s="45"/>
+      <c r="O90" s="45"/>
+      <c r="P90" s="45"/>
+      <c r="Q90" s="45"/>
+      <c r="R90" s="45"/>
+      <c r="S90" s="45"/>
+      <c r="T90" s="45"/>
+      <c r="U90" s="45"/>
+      <c r="V90" s="45"/>
+      <c r="W90" s="45"/>
+      <c r="X90" s="45"/>
+      <c r="Y90" s="45"/>
+      <c r="Z90" s="45"/>
+      <c r="AA90" s="45"/>
+    </row>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C91" s="10"/>
@@ -19906,11 +20121,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="10"/>
@@ -19975,11 +20190,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C93" s="10"/>
@@ -20044,11 +20259,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C94" s="10"/>
@@ -20113,11 +20328,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C95" s="10"/>
@@ -20182,11 +20397,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C96" s="10"/>
@@ -20251,11 +20466,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="38">
+    <row r="97" spans="1:27" ht="19.5">
+      <c r="A97" s="35">
         <v>9</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="50" t="s">
         <v>88</v>
       </c>
       <c r="C97" s="10"/>
@@ -20320,11 +20535,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="50" t="s">
         <v>89</v>
       </c>
       <c r="C98" s="10"/>
@@ -20389,11 +20604,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="10"/>
@@ -20458,11 +20673,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="38">
+    <row r="100" spans="1:27" ht="19.5">
+      <c r="A100" s="35">
         <v>9</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="50" t="s">
         <v>90</v>
       </c>
       <c r="C100" s="10"/>
@@ -20527,11 +20742,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C101" s="10"/>
@@ -20596,12 +20811,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1">
+      <c r="A102" s="45"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="45"/>
+      <c r="D102" s="45"/>
+      <c r="E102" s="45"/>
+      <c r="F102" s="45"/>
+      <c r="G102" s="45"/>
+      <c r="H102" s="45"/>
+      <c r="I102" s="45"/>
+      <c r="J102" s="45"/>
+      <c r="K102" s="45"/>
+      <c r="L102" s="45"/>
+      <c r="M102" s="45"/>
+      <c r="N102" s="45"/>
+      <c r="O102" s="45"/>
+      <c r="P102" s="45"/>
+      <c r="Q102" s="45"/>
+      <c r="R102" s="45"/>
+      <c r="S102" s="45"/>
+      <c r="T102" s="45"/>
+      <c r="U102" s="45"/>
+      <c r="V102" s="45"/>
+      <c r="W102" s="45"/>
+      <c r="X102" s="45"/>
+      <c r="Y102" s="45"/>
+      <c r="Z102" s="45"/>
+      <c r="AA102" s="45"/>
+    </row>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C103" s="10"/>
@@ -20666,11 +20909,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="10"/>
@@ -20735,11 +20978,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C105" s="10"/>
@@ -20804,11 +21047,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C106" s="10"/>
@@ -20873,11 +21116,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C107" s="10"/>
@@ -20942,11 +21185,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="10"/>
@@ -21011,11 +21254,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
-      <c r="A109" s="38">
+    <row r="109" spans="1:27" ht="19.5">
+      <c r="A109" s="35">
         <v>10</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="50" t="s">
         <v>88</v>
       </c>
       <c r="C109" s="10"/>
@@ -21080,11 +21323,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="50" t="s">
         <v>89</v>
       </c>
       <c r="C110" s="10"/>
@@ -21149,11 +21392,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C111" s="10"/>
@@ -21218,11 +21461,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
-      <c r="A112" s="38">
+    <row r="112" spans="1:27" ht="19.5">
+      <c r="A112" s="35">
         <v>10</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="50" t="s">
         <v>90</v>
       </c>
       <c r="C112" s="10"/>
@@ -21287,11 +21530,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C113" s="10"/>
@@ -21356,12 +21599,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1">
+      <c r="A114" s="45"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="45"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
+      <c r="J114" s="45"/>
+      <c r="K114" s="45"/>
+      <c r="L114" s="45"/>
+      <c r="M114" s="45"/>
+      <c r="N114" s="45"/>
+      <c r="O114" s="45"/>
+      <c r="P114" s="45"/>
+      <c r="Q114" s="45"/>
+      <c r="R114" s="45"/>
+      <c r="S114" s="45"/>
+      <c r="T114" s="45"/>
+      <c r="U114" s="45"/>
+      <c r="V114" s="45"/>
+      <c r="W114" s="45"/>
+      <c r="X114" s="45"/>
+      <c r="Y114" s="45"/>
+      <c r="Z114" s="45"/>
+      <c r="AA114" s="45"/>
+    </row>
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="1"/>
@@ -21426,11 +21697,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="46" t="s">
         <v>25</v>
       </c>
       <c r="C116" s="1"/>
@@ -21495,11 +21766,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="46" t="s">
         <v>26</v>
       </c>
       <c r="C117" s="1"/>
@@ -21564,11 +21835,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="46" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="1"/>
@@ -21633,11 +21904,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="46" t="s">
         <v>28</v>
       </c>
       <c r="C119" s="1"/>
@@ -21702,11 +21973,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="46" t="s">
         <v>29</v>
       </c>
       <c r="C120" s="1"/>
@@ -21771,11 +22042,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="46" t="s">
         <v>30</v>
       </c>
       <c r="C121" s="1"/>
@@ -21840,11 +22111,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="46" t="s">
         <v>31</v>
       </c>
       <c r="C122" s="1"/>
@@ -21909,696 +22180,544 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="123" spans="1:28" s="7" customFormat="1">
+      <c r="A123" s="45"/>
+      <c r="B123" s="45"/>
+      <c r="C123" s="45"/>
+      <c r="D123" s="45"/>
+      <c r="E123" s="45"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="45"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="45"/>
+      <c r="J123" s="45"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="45"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="45"/>
+      <c r="O123" s="45"/>
+      <c r="P123" s="45"/>
+      <c r="Q123" s="45"/>
+      <c r="R123" s="45"/>
+      <c r="S123" s="45"/>
+      <c r="T123" s="45"/>
+      <c r="U123" s="45"/>
+      <c r="V123" s="45"/>
+      <c r="W123" s="45"/>
+      <c r="X123" s="45"/>
+      <c r="Y123" s="45"/>
+      <c r="Z123" s="45"/>
+      <c r="AA123" s="45"/>
+    </row>
     <row r="124" spans="1:28">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="7"/>
-      <c r="V124" s="7"/>
-      <c r="W124" s="7"/>
-      <c r="X124" s="7"/>
-      <c r="Y124" s="7"/>
-      <c r="Z124" s="7"/>
-      <c r="AA124" s="7"/>
+      <c r="A124" s="45"/>
+      <c r="B124" s="45"/>
+      <c r="C124" s="45"/>
+      <c r="D124" s="45"/>
+      <c r="E124" s="45"/>
+      <c r="F124" s="45"/>
+      <c r="G124" s="45"/>
+      <c r="H124" s="45"/>
+      <c r="I124" s="45"/>
+      <c r="J124" s="45"/>
+      <c r="K124" s="45"/>
+      <c r="L124" s="45"/>
+      <c r="M124" s="45"/>
+      <c r="N124" s="45"/>
+      <c r="O124" s="45"/>
+      <c r="P124" s="45"/>
+      <c r="Q124" s="45"/>
+      <c r="R124" s="45"/>
+      <c r="S124" s="45"/>
+      <c r="T124" s="45"/>
+      <c r="U124" s="45"/>
+      <c r="V124" s="45"/>
+      <c r="W124" s="45"/>
+      <c r="X124" s="45"/>
+      <c r="Y124" s="45"/>
+      <c r="Z124" s="45"/>
+      <c r="AA124" s="45"/>
       <c r="AB124" s="7"/>
     </row>
     <row r="125" spans="1:28">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="7"/>
-      <c r="T125" s="7"/>
-      <c r="U125" s="7"/>
-      <c r="V125" s="7"/>
-      <c r="W125" s="7"/>
-      <c r="X125" s="7"/>
-      <c r="Y125" s="7"/>
-      <c r="Z125" s="7"/>
-      <c r="AA125" s="7"/>
+      <c r="A125" s="45"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="45"/>
+      <c r="D125" s="45"/>
+      <c r="E125" s="45"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="45"/>
+      <c r="I125" s="45"/>
+      <c r="J125" s="45"/>
+      <c r="K125" s="45"/>
+      <c r="L125" s="45"/>
+      <c r="M125" s="45"/>
+      <c r="N125" s="45"/>
+      <c r="O125" s="45"/>
+      <c r="P125" s="45"/>
+      <c r="Q125" s="45"/>
+      <c r="R125" s="45"/>
+      <c r="S125" s="45"/>
+      <c r="T125" s="45"/>
+      <c r="U125" s="45"/>
+      <c r="V125" s="45"/>
+      <c r="W125" s="45"/>
+      <c r="X125" s="45"/>
+      <c r="Y125" s="45"/>
+      <c r="Z125" s="45"/>
+      <c r="AA125" s="45"/>
       <c r="AB125" s="7"/>
     </row>
     <row r="126" spans="1:28">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="7"/>
-      <c r="T126" s="7"/>
-      <c r="U126" s="7"/>
-      <c r="V126" s="7"/>
-      <c r="W126" s="7"/>
-      <c r="X126" s="7"/>
-      <c r="Y126" s="7"/>
-      <c r="Z126" s="7"/>
-      <c r="AA126" s="7"/>
+      <c r="A126" s="45"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="45"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="45"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="45"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="45"/>
+      <c r="J126" s="45"/>
+      <c r="K126" s="45"/>
+      <c r="L126" s="45"/>
+      <c r="M126" s="45"/>
+      <c r="N126" s="45"/>
+      <c r="O126" s="45"/>
+      <c r="P126" s="45"/>
+      <c r="Q126" s="45"/>
+      <c r="R126" s="45"/>
+      <c r="S126" s="45"/>
+      <c r="T126" s="45"/>
+      <c r="U126" s="45"/>
+      <c r="V126" s="45"/>
+      <c r="W126" s="45"/>
+      <c r="X126" s="45"/>
+      <c r="Y126" s="45"/>
+      <c r="Z126" s="45"/>
+      <c r="AA126" s="45"/>
       <c r="AB126" s="7"/>
     </row>
     <row r="127" spans="1:28">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="7"/>
-      <c r="S127" s="7"/>
-      <c r="T127" s="7"/>
-      <c r="U127" s="7"/>
-      <c r="V127" s="7"/>
-      <c r="W127" s="7"/>
-      <c r="X127" s="7"/>
-      <c r="Y127" s="7"/>
-      <c r="Z127" s="7"/>
-      <c r="AA127" s="7"/>
+      <c r="A127" s="45"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="45"/>
+      <c r="D127" s="45"/>
+      <c r="E127" s="45"/>
+      <c r="F127" s="45"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="45"/>
+      <c r="I127" s="45"/>
+      <c r="J127" s="45"/>
+      <c r="K127" s="45"/>
+      <c r="L127" s="45"/>
+      <c r="M127" s="45"/>
+      <c r="N127" s="45"/>
+      <c r="O127" s="45"/>
+      <c r="P127" s="45"/>
+      <c r="Q127" s="45"/>
+      <c r="R127" s="45"/>
+      <c r="S127" s="45"/>
+      <c r="T127" s="45"/>
+      <c r="U127" s="45"/>
+      <c r="V127" s="45"/>
+      <c r="W127" s="45"/>
+      <c r="X127" s="45"/>
+      <c r="Y127" s="45"/>
+      <c r="Z127" s="45"/>
+      <c r="AA127" s="45"/>
       <c r="AB127" s="7"/>
     </row>
     <row r="128" spans="1:28">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="7"/>
-      <c r="T128" s="7"/>
-      <c r="U128" s="7"/>
-      <c r="V128" s="7"/>
-      <c r="W128" s="7"/>
-      <c r="X128" s="7"/>
-      <c r="Y128" s="7"/>
-      <c r="Z128" s="7"/>
-      <c r="AA128" s="7"/>
+      <c r="A128" s="45"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="45"/>
+      <c r="D128" s="45"/>
+      <c r="E128" s="45"/>
+      <c r="F128" s="45"/>
+      <c r="G128" s="45"/>
+      <c r="H128" s="45"/>
+      <c r="I128" s="45"/>
+      <c r="J128" s="45"/>
+      <c r="K128" s="45"/>
+      <c r="L128" s="45"/>
+      <c r="M128" s="45"/>
+      <c r="N128" s="45"/>
+      <c r="O128" s="45"/>
+      <c r="P128" s="45"/>
+      <c r="Q128" s="45"/>
+      <c r="R128" s="45"/>
+      <c r="S128" s="45"/>
+      <c r="T128" s="45"/>
+      <c r="U128" s="45"/>
+      <c r="V128" s="45"/>
+      <c r="W128" s="45"/>
+      <c r="X128" s="45"/>
+      <c r="Y128" s="45"/>
+      <c r="Z128" s="45"/>
+      <c r="AA128" s="45"/>
       <c r="AB128" s="7"/>
     </row>
     <row r="129" spans="1:28">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="7"/>
-      <c r="T129" s="7"/>
-      <c r="U129" s="7"/>
-      <c r="V129" s="7"/>
-      <c r="W129" s="7"/>
-      <c r="X129" s="7"/>
-      <c r="Y129" s="7"/>
-      <c r="Z129" s="7"/>
-      <c r="AA129" s="7"/>
+      <c r="A129" s="45"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="45"/>
+      <c r="D129" s="45"/>
+      <c r="E129" s="45"/>
+      <c r="F129" s="45"/>
+      <c r="G129" s="45"/>
+      <c r="H129" s="45"/>
+      <c r="I129" s="45"/>
+      <c r="J129" s="45"/>
+      <c r="K129" s="45"/>
+      <c r="L129" s="45"/>
+      <c r="M129" s="45"/>
+      <c r="N129" s="45"/>
+      <c r="O129" s="45"/>
+      <c r="P129" s="45"/>
+      <c r="Q129" s="45"/>
+      <c r="R129" s="45"/>
+      <c r="S129" s="45"/>
+      <c r="T129" s="45"/>
+      <c r="U129" s="45"/>
+      <c r="V129" s="45"/>
+      <c r="W129" s="45"/>
+      <c r="X129" s="45"/>
+      <c r="Y129" s="45"/>
+      <c r="Z129" s="45"/>
+      <c r="AA129" s="45"/>
       <c r="AB129" s="7"/>
     </row>
     <row r="130" spans="1:28">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="7"/>
-      <c r="T130" s="7"/>
-      <c r="U130" s="7"/>
-      <c r="V130" s="7"/>
-      <c r="W130" s="7"/>
-      <c r="X130" s="7"/>
-      <c r="Y130" s="7"/>
-      <c r="Z130" s="7"/>
-      <c r="AA130" s="7"/>
+      <c r="A130" s="45"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="45"/>
+      <c r="D130" s="45"/>
+      <c r="E130" s="45"/>
+      <c r="F130" s="45"/>
+      <c r="G130" s="45"/>
+      <c r="H130" s="45"/>
+      <c r="I130" s="45"/>
+      <c r="J130" s="45"/>
+      <c r="K130" s="45"/>
+      <c r="L130" s="45"/>
+      <c r="M130" s="45"/>
+      <c r="N130" s="45"/>
+      <c r="O130" s="45"/>
+      <c r="P130" s="45"/>
+      <c r="Q130" s="45"/>
+      <c r="R130" s="45"/>
+      <c r="S130" s="45"/>
+      <c r="T130" s="45"/>
+      <c r="U130" s="45"/>
+      <c r="V130" s="45"/>
+      <c r="W130" s="45"/>
+      <c r="X130" s="45"/>
+      <c r="Y130" s="45"/>
+      <c r="Z130" s="45"/>
+      <c r="AA130" s="45"/>
       <c r="AB130" s="7"/>
     </row>
     <row r="131" spans="1:28">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="7"/>
-      <c r="T131" s="7"/>
-      <c r="U131" s="7"/>
-      <c r="V131" s="7"/>
-      <c r="W131" s="7"/>
-      <c r="X131" s="7"/>
-      <c r="Y131" s="7"/>
-      <c r="Z131" s="7"/>
-      <c r="AA131" s="7"/>
+      <c r="A131" s="45"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="45"/>
+      <c r="D131" s="45"/>
+      <c r="E131" s="45"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="45"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="45"/>
+      <c r="J131" s="45"/>
+      <c r="K131" s="45"/>
+      <c r="L131" s="45"/>
+      <c r="M131" s="45"/>
+      <c r="N131" s="45"/>
+      <c r="O131" s="45"/>
+      <c r="P131" s="45"/>
+      <c r="Q131" s="45"/>
+      <c r="R131" s="45"/>
+      <c r="S131" s="45"/>
+      <c r="T131" s="45"/>
+      <c r="U131" s="45"/>
+      <c r="V131" s="45"/>
+      <c r="W131" s="45"/>
+      <c r="X131" s="45"/>
+      <c r="Y131" s="45"/>
+      <c r="Z131" s="45"/>
+      <c r="AA131" s="45"/>
       <c r="AB131" s="7"/>
     </row>
     <row r="132" spans="1:28">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="7"/>
-      <c r="T132" s="7"/>
-      <c r="U132" s="7"/>
-      <c r="V132" s="7"/>
-      <c r="W132" s="7"/>
-      <c r="X132" s="7"/>
-      <c r="Y132" s="7"/>
-      <c r="Z132" s="7"/>
-      <c r="AA132" s="7"/>
+      <c r="A132" s="45"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="45"/>
+      <c r="D132" s="45"/>
+      <c r="E132" s="45"/>
+      <c r="F132" s="45"/>
+      <c r="G132" s="45"/>
+      <c r="H132" s="45"/>
+      <c r="I132" s="45"/>
+      <c r="J132" s="45"/>
+      <c r="K132" s="45"/>
+      <c r="L132" s="45"/>
+      <c r="M132" s="45"/>
+      <c r="N132" s="45"/>
+      <c r="O132" s="45"/>
+      <c r="P132" s="45"/>
+      <c r="Q132" s="45"/>
+      <c r="R132" s="45"/>
+      <c r="S132" s="45"/>
+      <c r="T132" s="45"/>
+      <c r="U132" s="45"/>
+      <c r="V132" s="45"/>
+      <c r="W132" s="45"/>
+      <c r="X132" s="45"/>
+      <c r="Y132" s="45"/>
+      <c r="Z132" s="45"/>
+      <c r="AA132" s="45"/>
       <c r="AB132" s="7"/>
     </row>
     <row r="133" spans="1:28">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="7"/>
-      <c r="T133" s="7"/>
-      <c r="U133" s="7"/>
-      <c r="V133" s="7"/>
-      <c r="W133" s="7"/>
-      <c r="X133" s="7"/>
-      <c r="Y133" s="7"/>
-      <c r="Z133" s="7"/>
-      <c r="AA133" s="7"/>
+      <c r="A133" s="45"/>
+      <c r="B133" s="45"/>
+      <c r="C133" s="45"/>
+      <c r="D133" s="45"/>
+      <c r="E133" s="45"/>
+      <c r="F133" s="45"/>
+      <c r="G133" s="45"/>
+      <c r="H133" s="45"/>
+      <c r="I133" s="45"/>
+      <c r="J133" s="45"/>
+      <c r="K133" s="45"/>
+      <c r="L133" s="45"/>
+      <c r="M133" s="45"/>
+      <c r="N133" s="45"/>
+      <c r="O133" s="45"/>
+      <c r="P133" s="45"/>
+      <c r="Q133" s="45"/>
+      <c r="R133" s="45"/>
+      <c r="S133" s="45"/>
+      <c r="T133" s="45"/>
+      <c r="U133" s="45"/>
+      <c r="V133" s="45"/>
+      <c r="W133" s="45"/>
+      <c r="X133" s="45"/>
+      <c r="Y133" s="45"/>
+      <c r="Z133" s="45"/>
+      <c r="AA133" s="45"/>
       <c r="AB133" s="7"/>
     </row>
     <row r="134" spans="1:28">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="7"/>
-      <c r="T134" s="7"/>
-      <c r="U134" s="7"/>
-      <c r="V134" s="7"/>
-      <c r="W134" s="7"/>
-      <c r="X134" s="7"/>
-      <c r="Y134" s="7"/>
-      <c r="Z134" s="7"/>
-      <c r="AA134" s="7"/>
+      <c r="A134" s="45"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="45"/>
+      <c r="E134" s="45"/>
+      <c r="F134" s="45"/>
+      <c r="G134" s="45"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="45"/>
+      <c r="J134" s="45"/>
+      <c r="K134" s="45"/>
+      <c r="L134" s="45"/>
+      <c r="M134" s="45"/>
+      <c r="N134" s="45"/>
+      <c r="O134" s="45"/>
+      <c r="P134" s="45"/>
+      <c r="Q134" s="45"/>
+      <c r="R134" s="45"/>
+      <c r="S134" s="45"/>
+      <c r="T134" s="45"/>
+      <c r="U134" s="45"/>
+      <c r="V134" s="45"/>
+      <c r="W134" s="45"/>
+      <c r="X134" s="45"/>
+      <c r="Y134" s="45"/>
+      <c r="Z134" s="45"/>
+      <c r="AA134" s="45"/>
       <c r="AB134" s="7"/>
     </row>
     <row r="135" spans="1:28">
-      <c r="A135" s="7"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="7"/>
-      <c r="S135" s="7"/>
-      <c r="T135" s="7"/>
-      <c r="U135" s="7"/>
-      <c r="V135" s="7"/>
-      <c r="W135" s="7"/>
-      <c r="X135" s="7"/>
-      <c r="Y135" s="7"/>
-      <c r="Z135" s="7"/>
-      <c r="AA135" s="7"/>
+      <c r="A135" s="45"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="45"/>
+      <c r="D135" s="45"/>
+      <c r="E135" s="45"/>
+      <c r="F135" s="45"/>
+      <c r="G135" s="45"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="45"/>
+      <c r="J135" s="45"/>
+      <c r="K135" s="45"/>
+      <c r="L135" s="45"/>
+      <c r="M135" s="45"/>
+      <c r="N135" s="45"/>
+      <c r="O135" s="45"/>
+      <c r="P135" s="45"/>
+      <c r="Q135" s="45"/>
+      <c r="R135" s="45"/>
+      <c r="S135" s="45"/>
+      <c r="T135" s="45"/>
+      <c r="U135" s="45"/>
+      <c r="V135" s="45"/>
+      <c r="W135" s="45"/>
+      <c r="X135" s="45"/>
+      <c r="Y135" s="45"/>
+      <c r="Z135" s="45"/>
+      <c r="AA135" s="45"/>
       <c r="AB135" s="7"/>
     </row>
     <row r="136" spans="1:28">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="7"/>
-      <c r="T136" s="7"/>
-      <c r="U136" s="7"/>
-      <c r="V136" s="7"/>
-      <c r="W136" s="7"/>
-      <c r="X136" s="7"/>
-      <c r="Y136" s="7"/>
-      <c r="Z136" s="7"/>
-      <c r="AA136" s="7"/>
+      <c r="A136" s="45"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="45"/>
+      <c r="D136" s="45"/>
+      <c r="E136" s="45"/>
+      <c r="F136" s="45"/>
+      <c r="G136" s="45"/>
+      <c r="H136" s="45"/>
+      <c r="I136" s="45"/>
+      <c r="J136" s="45"/>
+      <c r="K136" s="45"/>
+      <c r="L136" s="45"/>
+      <c r="M136" s="45"/>
+      <c r="N136" s="45"/>
+      <c r="O136" s="45"/>
+      <c r="P136" s="45"/>
+      <c r="Q136" s="45"/>
+      <c r="R136" s="45"/>
+      <c r="S136" s="45"/>
+      <c r="T136" s="45"/>
+      <c r="U136" s="45"/>
+      <c r="V136" s="45"/>
+      <c r="W136" s="45"/>
+      <c r="X136" s="45"/>
+      <c r="Y136" s="45"/>
+      <c r="Z136" s="45"/>
+      <c r="AA136" s="45"/>
       <c r="AB136" s="7"/>
     </row>
     <row r="137" spans="1:28">
-      <c r="A137" s="7"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="7"/>
-      <c r="T137" s="7"/>
-      <c r="U137" s="7"/>
-      <c r="V137" s="7"/>
-      <c r="W137" s="7"/>
-      <c r="X137" s="7"/>
-      <c r="Y137" s="7"/>
-      <c r="Z137" s="7"/>
-      <c r="AA137" s="7"/>
+      <c r="A137" s="45"/>
+      <c r="B137" s="45"/>
+      <c r="C137" s="45"/>
+      <c r="D137" s="45"/>
+      <c r="E137" s="45"/>
+      <c r="F137" s="45"/>
+      <c r="G137" s="45"/>
+      <c r="H137" s="45"/>
+      <c r="I137" s="45"/>
+      <c r="J137" s="45"/>
+      <c r="K137" s="45"/>
+      <c r="L137" s="45"/>
+      <c r="M137" s="45"/>
+      <c r="N137" s="45"/>
+      <c r="O137" s="45"/>
+      <c r="P137" s="45"/>
+      <c r="Q137" s="45"/>
+      <c r="R137" s="45"/>
+      <c r="S137" s="45"/>
+      <c r="T137" s="45"/>
+      <c r="U137" s="45"/>
+      <c r="V137" s="45"/>
+      <c r="W137" s="45"/>
+      <c r="X137" s="45"/>
+      <c r="Y137" s="45"/>
+      <c r="Z137" s="45"/>
+      <c r="AA137" s="45"/>
       <c r="AB137" s="7"/>
     </row>
     <row r="138" spans="1:28">
-      <c r="A138" s="7"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="7"/>
-      <c r="T138" s="7"/>
-      <c r="U138" s="7"/>
-      <c r="V138" s="7"/>
-      <c r="W138" s="7"/>
-      <c r="X138" s="7"/>
-      <c r="Y138" s="7"/>
-      <c r="Z138" s="7"/>
-      <c r="AA138" s="7"/>
+      <c r="A138" s="45"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="45"/>
+      <c r="D138" s="45"/>
+      <c r="E138" s="45"/>
+      <c r="F138" s="45"/>
+      <c r="G138" s="45"/>
+      <c r="H138" s="45"/>
+      <c r="I138" s="45"/>
+      <c r="J138" s="45"/>
+      <c r="K138" s="45"/>
+      <c r="L138" s="45"/>
+      <c r="M138" s="45"/>
+      <c r="N138" s="45"/>
+      <c r="O138" s="45"/>
+      <c r="P138" s="45"/>
+      <c r="Q138" s="45"/>
+      <c r="R138" s="45"/>
+      <c r="S138" s="45"/>
+      <c r="T138" s="45"/>
+      <c r="U138" s="45"/>
+      <c r="V138" s="45"/>
+      <c r="W138" s="45"/>
+      <c r="X138" s="45"/>
+      <c r="Y138" s="45"/>
+      <c r="Z138" s="45"/>
+      <c r="AA138" s="45"/>
       <c r="AB138" s="7"/>
     </row>
     <row r="139" spans="1:28">
-      <c r="A139" s="7"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7"/>
-      <c r="J139" s="7"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="7"/>
-      <c r="T139" s="7"/>
-      <c r="U139" s="7"/>
-      <c r="V139" s="7"/>
-      <c r="W139" s="7"/>
-      <c r="X139" s="7"/>
-      <c r="Y139" s="7"/>
-      <c r="Z139" s="7"/>
-      <c r="AA139" s="7"/>
+      <c r="A139" s="45"/>
+      <c r="B139" s="45"/>
+      <c r="C139" s="45"/>
+      <c r="D139" s="45"/>
+      <c r="E139" s="45"/>
+      <c r="F139" s="45"/>
+      <c r="G139" s="45"/>
+      <c r="H139" s="45"/>
+      <c r="I139" s="45"/>
+      <c r="J139" s="45"/>
+      <c r="K139" s="45"/>
+      <c r="L139" s="45"/>
+      <c r="M139" s="45"/>
+      <c r="N139" s="45"/>
+      <c r="O139" s="45"/>
+      <c r="P139" s="45"/>
+      <c r="Q139" s="45"/>
+      <c r="R139" s="45"/>
+      <c r="S139" s="45"/>
+      <c r="T139" s="45"/>
+      <c r="U139" s="45"/>
+      <c r="V139" s="45"/>
+      <c r="W139" s="45"/>
+      <c r="X139" s="45"/>
+      <c r="Y139" s="45"/>
+      <c r="Z139" s="45"/>
+      <c r="AA139" s="45"/>
       <c r="AB139" s="7"/>
     </row>
     <row r="140" spans="1:28">
-      <c r="A140" s="7"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="7"/>
-      <c r="S140" s="7"/>
-      <c r="T140" s="7"/>
-      <c r="U140" s="7"/>
-      <c r="V140" s="7"/>
-      <c r="W140" s="7"/>
-      <c r="X140" s="7"/>
-      <c r="Y140" s="7"/>
-      <c r="Z140" s="7"/>
-      <c r="AA140" s="7"/>
+      <c r="A140" s="45"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="45"/>
+      <c r="D140" s="45"/>
+      <c r="E140" s="45"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="45"/>
+      <c r="H140" s="45"/>
+      <c r="I140" s="45"/>
+      <c r="J140" s="45"/>
+      <c r="K140" s="45"/>
+      <c r="L140" s="45"/>
+      <c r="M140" s="45"/>
+      <c r="N140" s="45"/>
+      <c r="O140" s="45"/>
+      <c r="P140" s="45"/>
+      <c r="Q140" s="45"/>
+      <c r="R140" s="45"/>
+      <c r="S140" s="45"/>
+      <c r="T140" s="45"/>
+      <c r="U140" s="45"/>
+      <c r="V140" s="45"/>
+      <c r="W140" s="45"/>
+      <c r="X140" s="45"/>
+      <c r="Y140" s="45"/>
+      <c r="Z140" s="45"/>
+      <c r="AA140" s="45"/>
       <c r="AB140" s="7"/>
-    </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
     </row>
   </sheetData>
   <protectedRanges>
@@ -22623,8 +22742,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 M103:M113 M115:M122 Y12:Y19 S12:S19 M12:M19 M21:M29 S103:S113 S55:S65 S21:S29 S31:S41 M31:M41 Y103:Y113 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G40:G41 G51:G53 Y55:Y65 M55:M65 G103:G113 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 Y21:Y29" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 R55:R65 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 F103:F113 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L55:L65 R91:R101 R103:R113 R12:R19 R3:R10 R115:R122 F115:F122 F40:F41 F67:F77 F79:F89 F51:F53 L115:L122 F91:F101 X115:X122 X21:X29" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{70D3727D-338A-491B-857F-D45894F9B60E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
